--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -315,6 +315,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -894,7 +903,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -915,7 +924,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -933,9 +942,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="55" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
+      <c r="O2" s="58" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -315,6 +315,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -551,8 +569,11 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당자
-(직접 입력)</t>
+        <t>▣ 부서 담당자
+• 부서 내 실제 담당자 이름 입력
+  예: 정민규, 한재운, 이찬
+• 입력 시: PMS에도 자동 반영
+• 빈 칸: 부서 참여 확정, 담당자 미정</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -566,26 +587,46 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조립
-(직접 입력)</t>
+        <t>▣ 조립 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ TURN-ON
-(직접 입력)</t>
+        <t>▣ TURN-ON (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모
-(직접 입력)</t>
+        <t>▣ 메모 (부서 자유 입력)
+• 자유 텍스트 입력
+• 활용:
+  - 이슈사항 (예: 자재 결품, 외주 지연)
+  - 변경 요청 (예: 사양 변경, 납기 조정)
+  - 다른 부서·PM에게 공유할 정보
+• 대시보드 집계에는 미포함</t>
       </text>
     </comment>
   </commentList>
@@ -903,7 +944,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -924,7 +965,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -942,9 +983,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="58" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="O2" s="64" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,20 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -112,8 +124,13 @@
         <fgColor rgb="008B1E22"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,11 +196,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -360,6 +391,48 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -587,7 +660,8 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조립 (세부항목 진척률)
+        <t>▣ 부서
+시작일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
@@ -598,7 +672,8 @@
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ TURN-ON (세부항목 진척률)
+        <t>▣ 부서
+완료일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
@@ -937,14 +1012,14 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" style="43" min="12" max="12"/>
-    <col width="9" customWidth="1" style="43" min="13" max="13"/>
+    <col width="12" customWidth="1" style="43" min="12" max="12"/>
+    <col width="12" customWidth="1" style="43" min="13" max="13"/>
     <col width="10" customWidth="1" style="43" min="14" max="14"/>
     <col width="28" customWidth="1" style="43" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -965,7 +1040,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -983,9 +1058,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="64" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="O2" s="78" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:52</t>
         </is>
       </c>
     </row>
@@ -1045,14 +1120,14 @@
           <t>🔒자동</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1122,14 +1197,16 @@
           <t>전체진척률(%)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>조립</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>TURN-ON</t>
+      <c r="L4" s="72" t="inlineStr">
+        <is>
+          <t>부서
+시작일</t>
+        </is>
+      </c>
+      <c r="M4" s="72" t="inlineStr">
+        <is>
+          <t>부서
+완료일</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -1189,8 +1266,8 @@
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="22" t="n"/>
     </row>
@@ -1240,8 +1317,8 @@
       </c>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="14" t="inlineStr"/>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
       <c r="N6" s="13" t="n"/>
       <c r="O6" s="24" t="n"/>
     </row>
@@ -1291,8 +1368,8 @@
       </c>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="22" t="n"/>
     </row>
@@ -1342,8 +1419,8 @@
       </c>
       <c r="J8" s="13" t="n"/>
       <c r="K8" s="14" t="inlineStr"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
       <c r="N8" s="13" t="n"/>
       <c r="O8" s="24" t="n"/>
     </row>
@@ -1393,8 +1470,8 @@
       </c>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="22" t="n"/>
     </row>
@@ -1444,8 +1521,8 @@
       </c>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="14" t="inlineStr"/>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="15" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
       <c r="O10" s="24" t="n"/>
     </row>
@@ -1495,8 +1572,8 @@
       </c>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="22" t="n"/>
     </row>
@@ -1546,8 +1623,8 @@
       </c>
       <c r="J12" s="13" t="n"/>
       <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="15" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
       <c r="N12" s="13" t="n"/>
       <c r="O12" s="24" t="n"/>
     </row>
@@ -1597,8 +1674,8 @@
       </c>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
       <c r="O13" s="22" t="n"/>
     </row>
@@ -1648,8 +1725,8 @@
       </c>
       <c r="J14" s="13" t="n"/>
       <c r="K14" s="14" t="inlineStr"/>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="15" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
       <c r="O14" s="24" t="n"/>
     </row>
@@ -1699,8 +1776,8 @@
       </c>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="22" t="n"/>
     </row>
@@ -1750,8 +1827,8 @@
       </c>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
       <c r="O16" s="24" t="n"/>
     </row>
@@ -1801,8 +1878,8 @@
       </c>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="22" t="n"/>
     </row>
@@ -1852,8 +1929,8 @@
       </c>
       <c r="J18" s="13" t="n"/>
       <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
       <c r="O18" s="24" t="n"/>
     </row>
@@ -1903,8 +1980,8 @@
       </c>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="22" t="n"/>
     </row>
@@ -1954,8 +2031,8 @@
       </c>
       <c r="J20" s="13" t="n"/>
       <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
       <c r="N20" s="13" t="n"/>
       <c r="O20" s="24" t="n"/>
     </row>
@@ -2005,8 +2082,8 @@
       </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="22" t="n"/>
     </row>
@@ -2056,8 +2133,8 @@
       </c>
       <c r="J22" s="13" t="n"/>
       <c r="K22" s="14" t="inlineStr"/>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
       <c r="N22" s="13" t="n"/>
       <c r="O22" s="24" t="n"/>
     </row>
@@ -2107,8 +2184,8 @@
       </c>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="22" t="n"/>
     </row>
@@ -2158,8 +2235,8 @@
       </c>
       <c r="J24" s="13" t="n"/>
       <c r="K24" s="14" t="inlineStr"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
       <c r="O24" s="24" t="n"/>
     </row>
@@ -2209,8 +2286,8 @@
       </c>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="11" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="22" t="n"/>
     </row>
@@ -2260,8 +2337,8 @@
       </c>
       <c r="J26" s="13" t="n"/>
       <c r="K26" s="14" t="inlineStr"/>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
       <c r="N26" s="13" t="n"/>
       <c r="O26" s="24" t="n"/>
     </row>
@@ -2311,8 +2388,8 @@
       </c>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="11" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
       <c r="O27" s="22" t="n"/>
     </row>
@@ -2362,8 +2439,8 @@
       </c>
       <c r="J28" s="13" t="n"/>
       <c r="K28" s="14" t="inlineStr"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
       <c r="O28" s="24" t="n"/>
     </row>
@@ -2413,8 +2490,8 @@
       </c>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
       <c r="O29" s="22" t="n"/>
     </row>
@@ -2464,8 +2541,8 @@
       </c>
       <c r="J30" s="13" t="n"/>
       <c r="K30" s="14" t="inlineStr"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
       <c r="O30" s="24" t="n"/>
     </row>
@@ -2515,8 +2592,8 @@
       </c>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="22" t="n"/>
     </row>
@@ -2566,8 +2643,8 @@
       </c>
       <c r="J32" s="13" t="n"/>
       <c r="K32" s="14" t="inlineStr"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
       <c r="O32" s="24" t="n"/>
     </row>
@@ -2617,8 +2694,8 @@
       </c>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="22" t="n"/>
     </row>
@@ -2668,8 +2745,8 @@
       </c>
       <c r="J34" s="13" t="n"/>
       <c r="K34" s="14" t="inlineStr"/>
-      <c r="L34" s="15" t="n"/>
-      <c r="M34" s="15" t="n"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
       <c r="O34" s="24" t="n"/>
     </row>
@@ -2719,8 +2796,8 @@
       </c>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="11" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="22" t="n"/>
     </row>
@@ -2770,8 +2847,8 @@
       </c>
       <c r="J36" s="13" t="n"/>
       <c r="K36" s="14" t="inlineStr"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
       <c r="O36" s="24" t="n"/>
     </row>
@@ -2821,8 +2898,8 @@
       </c>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="22" t="n"/>
     </row>
@@ -2872,8 +2949,8 @@
       </c>
       <c r="J38" s="13" t="n"/>
       <c r="K38" s="14" t="inlineStr"/>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="15" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
       <c r="O38" s="24" t="n"/>
     </row>
@@ -2923,8 +3000,8 @@
       </c>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="11" t="n"/>
-      <c r="M39" s="11" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="22" t="n"/>
     </row>
@@ -2974,8 +3051,8 @@
       </c>
       <c r="J40" s="13" t="n"/>
       <c r="K40" s="14" t="inlineStr"/>
-      <c r="L40" s="15" t="n"/>
-      <c r="M40" s="15" t="n"/>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
       <c r="O40" s="24" t="n"/>
     </row>
@@ -3025,8 +3102,8 @@
       </c>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="11" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="22" t="n"/>
     </row>
@@ -3076,8 +3153,8 @@
       </c>
       <c r="J42" s="13" t="n"/>
       <c r="K42" s="14" t="inlineStr"/>
-      <c r="L42" s="15" t="n"/>
-      <c r="M42" s="15" t="n"/>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
       <c r="O42" s="24" t="n"/>
     </row>
@@ -3127,8 +3204,8 @@
       </c>
       <c r="J43" s="9" t="n"/>
       <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="11" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="22" t="n"/>
     </row>
@@ -3178,8 +3255,8 @@
       </c>
       <c r="J44" s="13" t="n"/>
       <c r="K44" s="14" t="inlineStr"/>
-      <c r="L44" s="15" t="n"/>
-      <c r="M44" s="15" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
       <c r="O44" s="24" t="n"/>
     </row>
@@ -3229,8 +3306,8 @@
       </c>
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="11" t="n"/>
-      <c r="M45" s="11" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="22" t="n"/>
     </row>
@@ -3280,8 +3357,8 @@
       </c>
       <c r="J46" s="13" t="n"/>
       <c r="K46" s="14" t="inlineStr"/>
-      <c r="L46" s="15" t="n"/>
-      <c r="M46" s="15" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
       <c r="O46" s="24" t="n"/>
     </row>
@@ -3331,8 +3408,8 @@
       </c>
       <c r="J47" s="9" t="n"/>
       <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="11" t="n"/>
-      <c r="M47" s="11" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="22" t="n"/>
     </row>
@@ -3382,8 +3459,8 @@
       </c>
       <c r="J48" s="13" t="n"/>
       <c r="K48" s="14" t="inlineStr"/>
-      <c r="L48" s="15" t="n"/>
-      <c r="M48" s="15" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
       <c r="O48" s="24" t="n"/>
     </row>
@@ -3433,8 +3510,8 @@
       </c>
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="11" t="n"/>
-      <c r="M49" s="11" t="n"/>
+      <c r="L49" s="9" t="n"/>
+      <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="22" t="n"/>
     </row>
@@ -3484,8 +3561,8 @@
       </c>
       <c r="J50" s="13" t="n"/>
       <c r="K50" s="14" t="inlineStr"/>
-      <c r="L50" s="15" t="n"/>
-      <c r="M50" s="15" t="n"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
       <c r="O50" s="24" t="n"/>
     </row>
@@ -3535,8 +3612,8 @@
       </c>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
+      <c r="L51" s="9" t="n"/>
+      <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="22" t="n"/>
     </row>
@@ -3586,8 +3663,8 @@
       </c>
       <c r="J52" s="13" t="n"/>
       <c r="K52" s="14" t="inlineStr"/>
-      <c r="L52" s="15" t="n"/>
-      <c r="M52" s="15" t="n"/>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
       <c r="O52" s="24" t="n"/>
     </row>
@@ -3637,8 +3714,8 @@
       </c>
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="11" t="n"/>
-      <c r="M53" s="11" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="22" t="n"/>
     </row>
@@ -3688,8 +3765,8 @@
       </c>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="14" t="inlineStr"/>
-      <c r="L54" s="15" t="n"/>
-      <c r="M54" s="15" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
       <c r="O54" s="24" t="n"/>
     </row>
@@ -3739,8 +3816,8 @@
       </c>
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="11" t="n"/>
+      <c r="L55" s="9" t="n"/>
+      <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="22" t="n"/>
     </row>
@@ -3790,8 +3867,8 @@
       </c>
       <c r="J56" s="13" t="n"/>
       <c r="K56" s="14" t="inlineStr"/>
-      <c r="L56" s="15" t="n"/>
-      <c r="M56" s="15" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
       <c r="O56" s="24" t="n"/>
     </row>
@@ -3841,8 +3918,8 @@
       </c>
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="11" t="n"/>
-      <c r="M57" s="11" t="n"/>
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
       <c r="O57" s="22" t="n"/>
     </row>
@@ -3892,8 +3969,8 @@
       </c>
       <c r="J58" s="13" t="n"/>
       <c r="K58" s="14" t="inlineStr"/>
-      <c r="L58" s="15" t="n"/>
-      <c r="M58" s="15" t="n"/>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="13" t="n"/>
       <c r="N58" s="13" t="n"/>
       <c r="O58" s="24" t="n"/>
     </row>
@@ -3943,8 +4020,8 @@
       </c>
       <c r="J59" s="9" t="n"/>
       <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="11" t="n"/>
-      <c r="M59" s="11" t="n"/>
+      <c r="L59" s="9" t="n"/>
+      <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
       <c r="O59" s="22" t="n"/>
     </row>
@@ -3994,8 +4071,8 @@
       </c>
       <c r="J60" s="13" t="n"/>
       <c r="K60" s="14" t="inlineStr"/>
-      <c r="L60" s="15" t="n"/>
-      <c r="M60" s="15" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="13" t="n"/>
       <c r="N60" s="13" t="n"/>
       <c r="O60" s="24" t="n"/>
     </row>
@@ -4045,8 +4122,8 @@
       </c>
       <c r="J61" s="9" t="n"/>
       <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="11" t="n"/>
-      <c r="M61" s="11" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n"/>
       <c r="O61" s="22" t="n"/>
     </row>
@@ -4096,8 +4173,8 @@
       </c>
       <c r="J62" s="13" t="n"/>
       <c r="K62" s="14" t="inlineStr"/>
-      <c r="L62" s="15" t="n"/>
-      <c r="M62" s="15" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="13" t="n"/>
       <c r="N62" s="13" t="n"/>
       <c r="O62" s="24" t="n"/>
     </row>
@@ -4147,8 +4224,8 @@
       </c>
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="11" t="n"/>
-      <c r="M63" s="11" t="n"/>
+      <c r="L63" s="9" t="n"/>
+      <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n"/>
       <c r="O63" s="22" t="n"/>
     </row>
@@ -4198,8 +4275,8 @@
       </c>
       <c r="J64" s="13" t="n"/>
       <c r="K64" s="14" t="inlineStr"/>
-      <c r="L64" s="15" t="n"/>
-      <c r="M64" s="15" t="n"/>
+      <c r="L64" s="13" t="n"/>
+      <c r="M64" s="13" t="n"/>
       <c r="N64" s="13" t="n"/>
       <c r="O64" s="24" t="n"/>
     </row>
@@ -4249,8 +4326,8 @@
       </c>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="11" t="n"/>
-      <c r="M65" s="11" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n"/>
       <c r="O65" s="22" t="n"/>
     </row>
@@ -4300,8 +4377,8 @@
       </c>
       <c r="J66" s="13" t="n"/>
       <c r="K66" s="14" t="inlineStr"/>
-      <c r="L66" s="15" t="n"/>
-      <c r="M66" s="15" t="n"/>
+      <c r="L66" s="13" t="n"/>
+      <c r="M66" s="13" t="n"/>
       <c r="N66" s="13" t="n"/>
       <c r="O66" s="24" t="n"/>
     </row>
@@ -4351,8 +4428,8 @@
       </c>
       <c r="J67" s="9" t="n"/>
       <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="11" t="n"/>
-      <c r="M67" s="11" t="n"/>
+      <c r="L67" s="9" t="n"/>
+      <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n"/>
       <c r="O67" s="22" t="n"/>
     </row>
@@ -4402,8 +4479,8 @@
       </c>
       <c r="J68" s="13" t="n"/>
       <c r="K68" s="14" t="inlineStr"/>
-      <c r="L68" s="15" t="n"/>
-      <c r="M68" s="15" t="n"/>
+      <c r="L68" s="13" t="n"/>
+      <c r="M68" s="13" t="n"/>
       <c r="N68" s="13" t="n"/>
       <c r="O68" s="24" t="n"/>
     </row>
@@ -4453,8 +4530,8 @@
       </c>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="11" t="n"/>
-      <c r="M69" s="11" t="n"/>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n"/>
       <c r="O69" s="22" t="n"/>
     </row>
@@ -4504,8 +4581,8 @@
       </c>
       <c r="J70" s="13" t="n"/>
       <c r="K70" s="14" t="inlineStr"/>
-      <c r="L70" s="15" t="n"/>
-      <c r="M70" s="15" t="n"/>
+      <c r="L70" s="13" t="n"/>
+      <c r="M70" s="13" t="n"/>
       <c r="N70" s="13" t="n"/>
       <c r="O70" s="24" t="n"/>
     </row>
@@ -4555,8 +4632,8 @@
       </c>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="11" t="n"/>
-      <c r="M71" s="11" t="n"/>
+      <c r="L71" s="9" t="n"/>
+      <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n"/>
       <c r="O71" s="22" t="n"/>
     </row>
@@ -4606,8 +4683,8 @@
       </c>
       <c r="J72" s="13" t="n"/>
       <c r="K72" s="14" t="inlineStr"/>
-      <c r="L72" s="15" t="n"/>
-      <c r="M72" s="15" t="n"/>
+      <c r="L72" s="13" t="n"/>
+      <c r="M72" s="13" t="n"/>
       <c r="N72" s="13" t="n"/>
       <c r="O72" s="24" t="n"/>
     </row>
@@ -4657,8 +4734,8 @@
       </c>
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="11" t="n"/>
-      <c r="M73" s="11" t="n"/>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n"/>
       <c r="O73" s="22" t="n"/>
     </row>
@@ -4708,8 +4785,8 @@
       </c>
       <c r="J74" s="13" t="n"/>
       <c r="K74" s="14" t="inlineStr"/>
-      <c r="L74" s="15" t="n"/>
-      <c r="M74" s="15" t="n"/>
+      <c r="L74" s="13" t="n"/>
+      <c r="M74" s="13" t="n"/>
       <c r="N74" s="13" t="n"/>
       <c r="O74" s="24" t="n"/>
     </row>
@@ -4759,8 +4836,8 @@
       </c>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="11" t="n"/>
-      <c r="M75" s="11" t="n"/>
+      <c r="L75" s="9" t="n"/>
+      <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n"/>
       <c r="O75" s="22" t="n"/>
     </row>
@@ -4810,8 +4887,8 @@
       </c>
       <c r="J76" s="13" t="n"/>
       <c r="K76" s="14" t="inlineStr"/>
-      <c r="L76" s="15" t="n"/>
-      <c r="M76" s="15" t="n"/>
+      <c r="L76" s="13" t="n"/>
+      <c r="M76" s="13" t="n"/>
       <c r="N76" s="13" t="n"/>
       <c r="O76" s="24" t="n"/>
     </row>
@@ -4861,8 +4938,8 @@
       </c>
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
       <c r="O77" s="22" t="n"/>
     </row>
@@ -4912,8 +4989,8 @@
       </c>
       <c r="J78" s="13" t="n"/>
       <c r="K78" s="14" t="inlineStr"/>
-      <c r="L78" s="15" t="n"/>
-      <c r="M78" s="15" t="n"/>
+      <c r="L78" s="13" t="n"/>
+      <c r="M78" s="13" t="n"/>
       <c r="N78" s="13" t="n"/>
       <c r="O78" s="24" t="n"/>
     </row>
@@ -4963,8 +5040,8 @@
       </c>
       <c r="J79" s="9" t="n"/>
       <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
+      <c r="L79" s="9" t="n"/>
+      <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
       <c r="O79" s="22" t="n"/>
     </row>
@@ -5014,8 +5091,8 @@
       </c>
       <c r="J80" s="13" t="n"/>
       <c r="K80" s="14" t="inlineStr"/>
-      <c r="L80" s="15" t="n"/>
-      <c r="M80" s="15" t="n"/>
+      <c r="L80" s="13" t="n"/>
+      <c r="M80" s="13" t="n"/>
       <c r="N80" s="13" t="n"/>
       <c r="O80" s="24" t="n"/>
     </row>
@@ -5065,8 +5142,8 @@
       </c>
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
+      <c r="L81" s="9" t="n"/>
+      <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
       <c r="O81" s="22" t="n"/>
     </row>
@@ -5116,8 +5193,8 @@
       </c>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="14" t="inlineStr"/>
-      <c r="L82" s="15" t="n"/>
-      <c r="M82" s="15" t="n"/>
+      <c r="L82" s="13" t="n"/>
+      <c r="M82" s="13" t="n"/>
       <c r="N82" s="13" t="n"/>
       <c r="O82" s="24" t="n"/>
     </row>
@@ -5167,8 +5244,8 @@
       </c>
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
+      <c r="L83" s="9" t="n"/>
+      <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
       <c r="O83" s="22" t="n"/>
     </row>
@@ -5218,8 +5295,8 @@
       </c>
       <c r="J84" s="13" t="n"/>
       <c r="K84" s="14" t="inlineStr"/>
-      <c r="L84" s="15" t="n"/>
-      <c r="M84" s="15" t="n"/>
+      <c r="L84" s="13" t="n"/>
+      <c r="M84" s="13" t="n"/>
       <c r="N84" s="13" t="n"/>
       <c r="O84" s="24" t="n"/>
     </row>
@@ -5269,8 +5346,8 @@
       </c>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
+      <c r="L85" s="9" t="n"/>
+      <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
       <c r="O85" s="22" t="n"/>
     </row>
@@ -5320,8 +5397,8 @@
       </c>
       <c r="J86" s="13" t="n"/>
       <c r="K86" s="14" t="inlineStr"/>
-      <c r="L86" s="15" t="n"/>
-      <c r="M86" s="15" t="n"/>
+      <c r="L86" s="13" t="n"/>
+      <c r="M86" s="13" t="n"/>
       <c r="N86" s="13" t="n"/>
       <c r="O86" s="24" t="n"/>
     </row>
@@ -5371,8 +5448,8 @@
       </c>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="11" t="n"/>
-      <c r="M87" s="11" t="n"/>
+      <c r="L87" s="9" t="n"/>
+      <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
       <c r="O87" s="22" t="n"/>
     </row>
@@ -5422,8 +5499,8 @@
       </c>
       <c r="J88" s="13" t="n"/>
       <c r="K88" s="14" t="inlineStr"/>
-      <c r="L88" s="15" t="n"/>
-      <c r="M88" s="15" t="n"/>
+      <c r="L88" s="13" t="n"/>
+      <c r="M88" s="13" t="n"/>
       <c r="N88" s="13" t="n"/>
       <c r="O88" s="24" t="n"/>
     </row>
@@ -5473,8 +5550,8 @@
       </c>
       <c r="J89" s="9" t="n"/>
       <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="11" t="n"/>
-      <c r="M89" s="11" t="n"/>
+      <c r="L89" s="9" t="n"/>
+      <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
       <c r="O89" s="22" t="n"/>
     </row>
@@ -5524,8 +5601,8 @@
       </c>
       <c r="J90" s="13" t="n"/>
       <c r="K90" s="14" t="inlineStr"/>
-      <c r="L90" s="15" t="n"/>
-      <c r="M90" s="15" t="n"/>
+      <c r="L90" s="13" t="n"/>
+      <c r="M90" s="13" t="n"/>
       <c r="N90" s="13" t="n"/>
       <c r="O90" s="24" t="n"/>
     </row>
@@ -5575,8 +5652,8 @@
       </c>
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="10" t="inlineStr"/>
-      <c r="L91" s="11" t="n"/>
-      <c r="M91" s="11" t="n"/>
+      <c r="L91" s="9" t="n"/>
+      <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
       <c r="O91" s="22" t="n"/>
     </row>
@@ -5626,8 +5703,8 @@
       </c>
       <c r="J92" s="13" t="n"/>
       <c r="K92" s="14" t="inlineStr"/>
-      <c r="L92" s="15" t="n"/>
-      <c r="M92" s="15" t="n"/>
+      <c r="L92" s="13" t="n"/>
+      <c r="M92" s="13" t="n"/>
       <c r="N92" s="13" t="n"/>
       <c r="O92" s="24" t="n"/>
     </row>
@@ -5677,8 +5754,8 @@
       </c>
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="11" t="n"/>
-      <c r="M93" s="11" t="n"/>
+      <c r="L93" s="9" t="n"/>
+      <c r="M93" s="9" t="n"/>
       <c r="N93" s="9" t="n"/>
       <c r="O93" s="22" t="n"/>
     </row>
@@ -5728,8 +5805,8 @@
       </c>
       <c r="J94" s="13" t="n"/>
       <c r="K94" s="14" t="inlineStr"/>
-      <c r="L94" s="15" t="n"/>
-      <c r="M94" s="15" t="n"/>
+      <c r="L94" s="13" t="n"/>
+      <c r="M94" s="13" t="n"/>
       <c r="N94" s="13" t="n"/>
       <c r="O94" s="24" t="n"/>
     </row>
@@ -5779,8 +5856,8 @@
       </c>
       <c r="J95" s="9" t="n"/>
       <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="11" t="n"/>
-      <c r="M95" s="11" t="n"/>
+      <c r="L95" s="9" t="n"/>
+      <c r="M95" s="9" t="n"/>
       <c r="N95" s="9" t="n"/>
       <c r="O95" s="22" t="n"/>
     </row>
@@ -5830,8 +5907,8 @@
       </c>
       <c r="J96" s="13" t="n"/>
       <c r="K96" s="14" t="inlineStr"/>
-      <c r="L96" s="15" t="n"/>
-      <c r="M96" s="15" t="n"/>
+      <c r="L96" s="13" t="n"/>
+      <c r="M96" s="13" t="n"/>
       <c r="N96" s="13" t="n"/>
       <c r="O96" s="24" t="n"/>
     </row>
@@ -5881,8 +5958,8 @@
       </c>
       <c r="J97" s="9" t="n"/>
       <c r="K97" s="10" t="inlineStr"/>
-      <c r="L97" s="11" t="n"/>
-      <c r="M97" s="11" t="n"/>
+      <c r="L97" s="9" t="n"/>
+      <c r="M97" s="9" t="n"/>
       <c r="N97" s="9" t="n"/>
       <c r="O97" s="22" t="n"/>
     </row>
@@ -5932,8 +6009,8 @@
       </c>
       <c r="J98" s="13" t="n"/>
       <c r="K98" s="14" t="inlineStr"/>
-      <c r="L98" s="15" t="n"/>
-      <c r="M98" s="15" t="n"/>
+      <c r="L98" s="13" t="n"/>
+      <c r="M98" s="13" t="n"/>
       <c r="N98" s="13" t="n"/>
       <c r="O98" s="24" t="n"/>
     </row>
@@ -5983,8 +6060,8 @@
       </c>
       <c r="J99" s="9" t="n"/>
       <c r="K99" s="10" t="inlineStr"/>
-      <c r="L99" s="11" t="n"/>
-      <c r="M99" s="11" t="n"/>
+      <c r="L99" s="9" t="n"/>
+      <c r="M99" s="9" t="n"/>
       <c r="N99" s="9" t="n"/>
       <c r="O99" s="22" t="n"/>
     </row>
@@ -6034,8 +6111,8 @@
       </c>
       <c r="J100" s="13" t="n"/>
       <c r="K100" s="14" t="inlineStr"/>
-      <c r="L100" s="15" t="n"/>
-      <c r="M100" s="15" t="n"/>
+      <c r="L100" s="13" t="n"/>
+      <c r="M100" s="13" t="n"/>
       <c r="N100" s="13" t="n"/>
       <c r="O100" s="24" t="n"/>
     </row>
@@ -6085,8 +6162,8 @@
       </c>
       <c r="J101" s="9" t="n"/>
       <c r="K101" s="10" t="inlineStr"/>
-      <c r="L101" s="11" t="n"/>
-      <c r="M101" s="11" t="n"/>
+      <c r="L101" s="9" t="n"/>
+      <c r="M101" s="9" t="n"/>
       <c r="N101" s="9" t="n"/>
       <c r="O101" s="22" t="n"/>
     </row>
@@ -6136,8 +6213,8 @@
       </c>
       <c r="J102" s="13" t="n"/>
       <c r="K102" s="14" t="inlineStr"/>
-      <c r="L102" s="15" t="n"/>
-      <c r="M102" s="15" t="n"/>
+      <c r="L102" s="13" t="n"/>
+      <c r="M102" s="13" t="n"/>
       <c r="N102" s="13" t="n"/>
       <c r="O102" s="24" t="n"/>
     </row>
@@ -6187,8 +6264,8 @@
       </c>
       <c r="J103" s="9" t="n"/>
       <c r="K103" s="10" t="inlineStr"/>
-      <c r="L103" s="11" t="n"/>
-      <c r="M103" s="11" t="n"/>
+      <c r="L103" s="9" t="n"/>
+      <c r="M103" s="9" t="n"/>
       <c r="N103" s="9" t="n"/>
       <c r="O103" s="22" t="n"/>
     </row>
@@ -6238,8 +6315,8 @@
       </c>
       <c r="J104" s="13" t="n"/>
       <c r="K104" s="14" t="inlineStr"/>
-      <c r="L104" s="15" t="n"/>
-      <c r="M104" s="15" t="n"/>
+      <c r="L104" s="13" t="n"/>
+      <c r="M104" s="13" t="n"/>
       <c r="N104" s="13" t="n"/>
       <c r="O104" s="24" t="n"/>
     </row>
@@ -6289,8 +6366,8 @@
       </c>
       <c r="J105" s="9" t="n"/>
       <c r="K105" s="10" t="inlineStr"/>
-      <c r="L105" s="11" t="n"/>
-      <c r="M105" s="11" t="n"/>
+      <c r="L105" s="9" t="n"/>
+      <c r="M105" s="9" t="n"/>
       <c r="N105" s="9" t="n"/>
       <c r="O105" s="22" t="n"/>
     </row>
@@ -6340,8 +6417,8 @@
       </c>
       <c r="J106" s="13" t="n"/>
       <c r="K106" s="14" t="inlineStr"/>
-      <c r="L106" s="15" t="n"/>
-      <c r="M106" s="15" t="n"/>
+      <c r="L106" s="13" t="n"/>
+      <c r="M106" s="13" t="n"/>
       <c r="N106" s="13" t="n"/>
       <c r="O106" s="24" t="n"/>
     </row>
@@ -6391,8 +6468,8 @@
       </c>
       <c r="J107" s="9" t="n"/>
       <c r="K107" s="10" t="inlineStr"/>
-      <c r="L107" s="11" t="n"/>
-      <c r="M107" s="11" t="n"/>
+      <c r="L107" s="9" t="n"/>
+      <c r="M107" s="9" t="n"/>
       <c r="N107" s="9" t="n"/>
       <c r="O107" s="22" t="n"/>
     </row>
@@ -6442,8 +6519,8 @@
       </c>
       <c r="J108" s="13" t="n"/>
       <c r="K108" s="14" t="inlineStr"/>
-      <c r="L108" s="15" t="n"/>
-      <c r="M108" s="15" t="n"/>
+      <c r="L108" s="13" t="n"/>
+      <c r="M108" s="13" t="n"/>
       <c r="N108" s="13" t="n"/>
       <c r="O108" s="24" t="n"/>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -433,6 +433,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -660,26 +669,29 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서
-시작일 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        <t>▣ 부서 시작일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-10
+• 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
+• 부서가 ★실제로 작업을 시작한 날짜★ 기입
+• PO 후 작업 착수일 (지시 받은 날 아님)
+• 비워두면: 미착수 상태
+• v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
+  (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서
-완료일 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        <t>▣ 부서 완료일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-24
+• 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
+• 부서 작업이 ★실제로 완료된 날짜★ 기입
+• 예정일 아닌 ★실제 완료일★ 만 입력
+• 비워두면: PMS 진행현황에서 '미완료'로 집계
+• 입력 시: PMS 2_진행현황에 자동 표시 +
+  전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
+• '제외' 부서는 분모에서 제외됨</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
@@ -1019,7 +1031,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -1040,7 +1052,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1058,9 +1070,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="78" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:52</t>
+      <c r="O2" s="81" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -433,6 +433,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -660,11 +669,15 @@
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+• 자동 계산 (수정 불가, sync 시 갱신)
+• 시작일·완료일 입력 기반:
+    0%  = 미착수    (시작일·완료일 모두 빈 칸)
+   50%  = 진행중    (시작일만 입력)
+  100%  = 완료      (완료일까지 입력)
+• ★ 이 값은 '이 부서'만의 진척률입니다.
+• 프로젝트 전체 진척률은 PMS 1_프로젝트등록
+  '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1031,7 +1044,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -1052,7 +1065,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="80" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1070,9 +1083,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="O2" s="84" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:44</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1219,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>전체진척률(%)</t>
+          <t>부서진척률(%)</t>
         </is>
       </c>
       <c r="L4" s="72" t="inlineStr">
@@ -1277,7 +1290,9 @@
         </is>
       </c>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
@@ -1328,7 +1343,9 @@
         </is>
       </c>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="14" t="inlineStr"/>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="13" t="n"/>
       <c r="M6" s="13" t="n"/>
       <c r="N6" s="13" t="n"/>
@@ -1379,7 +1396,9 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
@@ -1430,7 +1449,9 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="13" t="n"/>
       <c r="M8" s="13" t="n"/>
       <c r="N8" s="13" t="n"/>
@@ -1481,7 +1502,9 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
@@ -1532,7 +1555,9 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
@@ -1583,7 +1608,9 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
@@ -1634,7 +1661,9 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
       <c r="N12" s="13" t="n"/>
@@ -1685,7 +1714,9 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
@@ -1736,7 +1767,9 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
@@ -1787,7 +1820,9 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
@@ -1838,7 +1873,9 @@
         </is>
       </c>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
@@ -1889,7 +1926,9 @@
         </is>
       </c>
       <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
@@ -1940,7 +1979,9 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="13" t="n"/>
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
@@ -1991,7 +2032,9 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
@@ -2042,7 +2085,9 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="13" t="n"/>
       <c r="M20" s="13" t="n"/>
       <c r="N20" s="13" t="n"/>
@@ -2093,7 +2138,9 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
@@ -2144,7 +2191,9 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="13" t="n"/>
       <c r="M22" s="13" t="n"/>
       <c r="N22" s="13" t="n"/>
@@ -2195,7 +2244,9 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
@@ -2246,7 +2297,9 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="13" t="n"/>
       <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
@@ -2297,7 +2350,9 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
@@ -2348,7 +2403,9 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="13" t="n"/>
       <c r="M26" s="13" t="n"/>
       <c r="N26" s="13" t="n"/>
@@ -2399,7 +2456,9 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
@@ -2450,7 +2509,9 @@
         </is>
       </c>
       <c r="J28" s="13" t="n"/>
-      <c r="K28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" s="13" t="n"/>
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
@@ -2501,7 +2562,9 @@
         </is>
       </c>
       <c r="J29" s="9" t="n"/>
-      <c r="K29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
@@ -2552,7 +2615,9 @@
         </is>
       </c>
       <c r="J30" s="13" t="n"/>
-      <c r="K30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" s="13" t="n"/>
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
@@ -2603,7 +2668,9 @@
         </is>
       </c>
       <c r="J31" s="9" t="n"/>
-      <c r="K31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
@@ -2654,7 +2721,9 @@
         </is>
       </c>
       <c r="J32" s="13" t="n"/>
-      <c r="K32" s="14" t="inlineStr"/>
+      <c r="K32" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" s="13" t="n"/>
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
@@ -2705,7 +2774,9 @@
         </is>
       </c>
       <c r="J33" s="9" t="n"/>
-      <c r="K33" s="10" t="inlineStr"/>
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
@@ -2756,7 +2827,9 @@
         </is>
       </c>
       <c r="J34" s="13" t="n"/>
-      <c r="K34" s="14" t="inlineStr"/>
+      <c r="K34" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L34" s="13" t="n"/>
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
@@ -2807,7 +2880,9 @@
         </is>
       </c>
       <c r="J35" s="9" t="n"/>
-      <c r="K35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
@@ -2858,7 +2933,9 @@
         </is>
       </c>
       <c r="J36" s="13" t="n"/>
-      <c r="K36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L36" s="13" t="n"/>
       <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
@@ -2909,7 +2986,9 @@
         </is>
       </c>
       <c r="J37" s="9" t="n"/>
-      <c r="K37" s="10" t="inlineStr"/>
+      <c r="K37" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
@@ -2960,7 +3039,9 @@
         </is>
       </c>
       <c r="J38" s="13" t="n"/>
-      <c r="K38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="13" t="n"/>
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
@@ -3011,7 +3092,9 @@
         </is>
       </c>
       <c r="J39" s="9" t="n"/>
-      <c r="K39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
@@ -3062,7 +3145,9 @@
         </is>
       </c>
       <c r="J40" s="13" t="n"/>
-      <c r="K40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L40" s="13" t="n"/>
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
@@ -3113,7 +3198,9 @@
         </is>
       </c>
       <c r="J41" s="9" t="n"/>
-      <c r="K41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
@@ -3164,7 +3251,9 @@
         </is>
       </c>
       <c r="J42" s="13" t="n"/>
-      <c r="K42" s="14" t="inlineStr"/>
+      <c r="K42" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="13" t="n"/>
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
@@ -3215,7 +3304,9 @@
         </is>
       </c>
       <c r="J43" s="9" t="n"/>
-      <c r="K43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
@@ -3266,7 +3357,9 @@
         </is>
       </c>
       <c r="J44" s="13" t="n"/>
-      <c r="K44" s="14" t="inlineStr"/>
+      <c r="K44" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" s="13" t="n"/>
       <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
@@ -3317,7 +3410,9 @@
         </is>
       </c>
       <c r="J45" s="9" t="n"/>
-      <c r="K45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
@@ -3368,7 +3463,9 @@
         </is>
       </c>
       <c r="J46" s="13" t="n"/>
-      <c r="K46" s="14" t="inlineStr"/>
+      <c r="K46" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" s="13" t="n"/>
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
@@ -3419,7 +3516,9 @@
         </is>
       </c>
       <c r="J47" s="9" t="n"/>
-      <c r="K47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
@@ -3470,7 +3569,9 @@
         </is>
       </c>
       <c r="J48" s="13" t="n"/>
-      <c r="K48" s="14" t="inlineStr"/>
+      <c r="K48" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L48" s="13" t="n"/>
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
@@ -3521,7 +3622,9 @@
         </is>
       </c>
       <c r="J49" s="9" t="n"/>
-      <c r="K49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
@@ -3572,7 +3675,9 @@
         </is>
       </c>
       <c r="J50" s="13" t="n"/>
-      <c r="K50" s="14" t="inlineStr"/>
+      <c r="K50" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L50" s="13" t="n"/>
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
@@ -3623,7 +3728,9 @@
         </is>
       </c>
       <c r="J51" s="9" t="n"/>
-      <c r="K51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
@@ -3674,7 +3781,9 @@
         </is>
       </c>
       <c r="J52" s="13" t="n"/>
-      <c r="K52" s="14" t="inlineStr"/>
+      <c r="K52" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" s="13" t="n"/>
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
@@ -3725,7 +3834,9 @@
         </is>
       </c>
       <c r="J53" s="9" t="n"/>
-      <c r="K53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
@@ -3776,7 +3887,9 @@
         </is>
       </c>
       <c r="J54" s="13" t="n"/>
-      <c r="K54" s="14" t="inlineStr"/>
+      <c r="K54" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" s="13" t="n"/>
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
@@ -3827,7 +3940,9 @@
         </is>
       </c>
       <c r="J55" s="9" t="n"/>
-      <c r="K55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
@@ -3878,7 +3993,9 @@
         </is>
       </c>
       <c r="J56" s="13" t="n"/>
-      <c r="K56" s="14" t="inlineStr"/>
+      <c r="K56" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L56" s="13" t="n"/>
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
@@ -3929,7 +4046,9 @@
         </is>
       </c>
       <c r="J57" s="9" t="n"/>
-      <c r="K57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
@@ -3980,7 +4099,9 @@
         </is>
       </c>
       <c r="J58" s="13" t="n"/>
-      <c r="K58" s="14" t="inlineStr"/>
+      <c r="K58" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" s="13" t="n"/>
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="13" t="n"/>
@@ -4031,7 +4152,9 @@
         </is>
       </c>
       <c r="J59" s="9" t="n"/>
-      <c r="K59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" s="9" t="n"/>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
@@ -4082,7 +4205,9 @@
         </is>
       </c>
       <c r="J60" s="13" t="n"/>
-      <c r="K60" s="14" t="inlineStr"/>
+      <c r="K60" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" s="13" t="n"/>
       <c r="M60" s="13" t="n"/>
       <c r="N60" s="13" t="n"/>
@@ -4133,7 +4258,9 @@
         </is>
       </c>
       <c r="J61" s="9" t="n"/>
-      <c r="K61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L61" s="9" t="n"/>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n"/>
@@ -4184,7 +4311,9 @@
         </is>
       </c>
       <c r="J62" s="13" t="n"/>
-      <c r="K62" s="14" t="inlineStr"/>
+      <c r="K62" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" s="13" t="n"/>
       <c r="M62" s="13" t="n"/>
       <c r="N62" s="13" t="n"/>
@@ -4235,7 +4364,9 @@
         </is>
       </c>
       <c r="J63" s="9" t="n"/>
-      <c r="K63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L63" s="9" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n"/>
@@ -4286,7 +4417,9 @@
         </is>
       </c>
       <c r="J64" s="13" t="n"/>
-      <c r="K64" s="14" t="inlineStr"/>
+      <c r="K64" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L64" s="13" t="n"/>
       <c r="M64" s="13" t="n"/>
       <c r="N64" s="13" t="n"/>
@@ -4337,7 +4470,9 @@
         </is>
       </c>
       <c r="J65" s="9" t="n"/>
-      <c r="K65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L65" s="9" t="n"/>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n"/>
@@ -4388,7 +4523,9 @@
         </is>
       </c>
       <c r="J66" s="13" t="n"/>
-      <c r="K66" s="14" t="inlineStr"/>
+      <c r="K66" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L66" s="13" t="n"/>
       <c r="M66" s="13" t="n"/>
       <c r="N66" s="13" t="n"/>
@@ -4439,7 +4576,9 @@
         </is>
       </c>
       <c r="J67" s="9" t="n"/>
-      <c r="K67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L67" s="9" t="n"/>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n"/>
@@ -4490,7 +4629,9 @@
         </is>
       </c>
       <c r="J68" s="13" t="n"/>
-      <c r="K68" s="14" t="inlineStr"/>
+      <c r="K68" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L68" s="13" t="n"/>
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="13" t="n"/>
@@ -4541,7 +4682,9 @@
         </is>
       </c>
       <c r="J69" s="9" t="n"/>
-      <c r="K69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" s="9" t="n"/>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n"/>
@@ -4592,7 +4735,9 @@
         </is>
       </c>
       <c r="J70" s="13" t="n"/>
-      <c r="K70" s="14" t="inlineStr"/>
+      <c r="K70" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L70" s="13" t="n"/>
       <c r="M70" s="13" t="n"/>
       <c r="N70" s="13" t="n"/>
@@ -4643,7 +4788,9 @@
         </is>
       </c>
       <c r="J71" s="9" t="n"/>
-      <c r="K71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L71" s="9" t="n"/>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n"/>
@@ -4694,7 +4841,9 @@
         </is>
       </c>
       <c r="J72" s="13" t="n"/>
-      <c r="K72" s="14" t="inlineStr"/>
+      <c r="K72" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L72" s="13" t="n"/>
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="13" t="n"/>
@@ -4745,7 +4894,9 @@
         </is>
       </c>
       <c r="J73" s="9" t="n"/>
-      <c r="K73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n"/>
@@ -4796,7 +4947,9 @@
         </is>
       </c>
       <c r="J74" s="13" t="n"/>
-      <c r="K74" s="14" t="inlineStr"/>
+      <c r="K74" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L74" s="13" t="n"/>
       <c r="M74" s="13" t="n"/>
       <c r="N74" s="13" t="n"/>
@@ -4847,7 +5000,9 @@
         </is>
       </c>
       <c r="J75" s="9" t="n"/>
-      <c r="K75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n"/>
@@ -4898,7 +5053,9 @@
         </is>
       </c>
       <c r="J76" s="13" t="n"/>
-      <c r="K76" s="14" t="inlineStr"/>
+      <c r="K76" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L76" s="13" t="n"/>
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="13" t="n"/>
@@ -4949,7 +5106,9 @@
         </is>
       </c>
       <c r="J77" s="9" t="n"/>
-      <c r="K77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
@@ -5000,7 +5159,9 @@
         </is>
       </c>
       <c r="J78" s="13" t="n"/>
-      <c r="K78" s="14" t="inlineStr"/>
+      <c r="K78" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L78" s="13" t="n"/>
       <c r="M78" s="13" t="n"/>
       <c r="N78" s="13" t="n"/>
@@ -5051,7 +5212,9 @@
         </is>
       </c>
       <c r="J79" s="9" t="n"/>
-      <c r="K79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
@@ -5102,7 +5265,9 @@
         </is>
       </c>
       <c r="J80" s="13" t="n"/>
-      <c r="K80" s="14" t="inlineStr"/>
+      <c r="K80" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L80" s="13" t="n"/>
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="13" t="n"/>
@@ -5153,7 +5318,9 @@
         </is>
       </c>
       <c r="J81" s="9" t="n"/>
-      <c r="K81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L81" s="9" t="n"/>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
@@ -5204,7 +5371,9 @@
         </is>
       </c>
       <c r="J82" s="13" t="n"/>
-      <c r="K82" s="14" t="inlineStr"/>
+      <c r="K82" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L82" s="13" t="n"/>
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="13" t="n"/>
@@ -5255,7 +5424,9 @@
         </is>
       </c>
       <c r="J83" s="9" t="n"/>
-      <c r="K83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L83" s="9" t="n"/>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
@@ -5306,7 +5477,9 @@
         </is>
       </c>
       <c r="J84" s="13" t="n"/>
-      <c r="K84" s="14" t="inlineStr"/>
+      <c r="K84" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L84" s="13" t="n"/>
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="13" t="n"/>
@@ -5357,7 +5530,9 @@
         </is>
       </c>
       <c r="J85" s="9" t="n"/>
-      <c r="K85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L85" s="9" t="n"/>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
@@ -5408,7 +5583,9 @@
         </is>
       </c>
       <c r="J86" s="13" t="n"/>
-      <c r="K86" s="14" t="inlineStr"/>
+      <c r="K86" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L86" s="13" t="n"/>
       <c r="M86" s="13" t="n"/>
       <c r="N86" s="13" t="n"/>
@@ -5459,7 +5636,9 @@
         </is>
       </c>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L87" s="9" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
@@ -5510,7 +5689,9 @@
         </is>
       </c>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="14" t="inlineStr"/>
+      <c r="K88" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L88" s="13" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="13" t="n"/>
@@ -5561,7 +5742,9 @@
         </is>
       </c>
       <c r="J89" s="9" t="n"/>
-      <c r="K89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L89" s="9" t="n"/>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
@@ -5612,7 +5795,9 @@
         </is>
       </c>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="14" t="inlineStr"/>
+      <c r="K90" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L90" s="13" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="13" t="n"/>
@@ -5663,7 +5848,9 @@
         </is>
       </c>
       <c r="J91" s="9" t="n"/>
-      <c r="K91" s="10" t="inlineStr"/>
+      <c r="K91" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" s="9" t="n"/>
       <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
@@ -5714,7 +5901,9 @@
         </is>
       </c>
       <c r="J92" s="13" t="n"/>
-      <c r="K92" s="14" t="inlineStr"/>
+      <c r="K92" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L92" s="13" t="n"/>
       <c r="M92" s="13" t="n"/>
       <c r="N92" s="13" t="n"/>
@@ -5765,7 +5954,9 @@
         </is>
       </c>
       <c r="J93" s="9" t="n"/>
-      <c r="K93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L93" s="9" t="n"/>
       <c r="M93" s="9" t="n"/>
       <c r="N93" s="9" t="n"/>
@@ -5816,7 +6007,9 @@
         </is>
       </c>
       <c r="J94" s="13" t="n"/>
-      <c r="K94" s="14" t="inlineStr"/>
+      <c r="K94" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L94" s="13" t="n"/>
       <c r="M94" s="13" t="n"/>
       <c r="N94" s="13" t="n"/>
@@ -5867,7 +6060,9 @@
         </is>
       </c>
       <c r="J95" s="9" t="n"/>
-      <c r="K95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L95" s="9" t="n"/>
       <c r="M95" s="9" t="n"/>
       <c r="N95" s="9" t="n"/>
@@ -5918,7 +6113,9 @@
         </is>
       </c>
       <c r="J96" s="13" t="n"/>
-      <c r="K96" s="14" t="inlineStr"/>
+      <c r="K96" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L96" s="13" t="n"/>
       <c r="M96" s="13" t="n"/>
       <c r="N96" s="13" t="n"/>
@@ -5969,7 +6166,9 @@
         </is>
       </c>
       <c r="J97" s="9" t="n"/>
-      <c r="K97" s="10" t="inlineStr"/>
+      <c r="K97" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L97" s="9" t="n"/>
       <c r="M97" s="9" t="n"/>
       <c r="N97" s="9" t="n"/>
@@ -6020,7 +6219,9 @@
         </is>
       </c>
       <c r="J98" s="13" t="n"/>
-      <c r="K98" s="14" t="inlineStr"/>
+      <c r="K98" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L98" s="13" t="n"/>
       <c r="M98" s="13" t="n"/>
       <c r="N98" s="13" t="n"/>
@@ -6071,7 +6272,9 @@
         </is>
       </c>
       <c r="J99" s="9" t="n"/>
-      <c r="K99" s="10" t="inlineStr"/>
+      <c r="K99" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L99" s="9" t="n"/>
       <c r="M99" s="9" t="n"/>
       <c r="N99" s="9" t="n"/>
@@ -6122,7 +6325,9 @@
         </is>
       </c>
       <c r="J100" s="13" t="n"/>
-      <c r="K100" s="14" t="inlineStr"/>
+      <c r="K100" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L100" s="13" t="n"/>
       <c r="M100" s="13" t="n"/>
       <c r="N100" s="13" t="n"/>
@@ -6173,7 +6378,9 @@
         </is>
       </c>
       <c r="J101" s="9" t="n"/>
-      <c r="K101" s="10" t="inlineStr"/>
+      <c r="K101" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L101" s="9" t="n"/>
       <c r="M101" s="9" t="n"/>
       <c r="N101" s="9" t="n"/>
@@ -6224,7 +6431,9 @@
         </is>
       </c>
       <c r="J102" s="13" t="n"/>
-      <c r="K102" s="14" t="inlineStr"/>
+      <c r="K102" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L102" s="13" t="n"/>
       <c r="M102" s="13" t="n"/>
       <c r="N102" s="13" t="n"/>
@@ -6275,7 +6484,9 @@
         </is>
       </c>
       <c r="J103" s="9" t="n"/>
-      <c r="K103" s="10" t="inlineStr"/>
+      <c r="K103" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L103" s="9" t="n"/>
       <c r="M103" s="9" t="n"/>
       <c r="N103" s="9" t="n"/>
@@ -6326,7 +6537,9 @@
         </is>
       </c>
       <c r="J104" s="13" t="n"/>
-      <c r="K104" s="14" t="inlineStr"/>
+      <c r="K104" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L104" s="13" t="n"/>
       <c r="M104" s="13" t="n"/>
       <c r="N104" s="13" t="n"/>
@@ -6377,7 +6590,9 @@
         </is>
       </c>
       <c r="J105" s="9" t="n"/>
-      <c r="K105" s="10" t="inlineStr"/>
+      <c r="K105" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" s="9" t="n"/>
       <c r="M105" s="9" t="n"/>
       <c r="N105" s="9" t="n"/>
@@ -6428,7 +6643,9 @@
         </is>
       </c>
       <c r="J106" s="13" t="n"/>
-      <c r="K106" s="14" t="inlineStr"/>
+      <c r="K106" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L106" s="13" t="n"/>
       <c r="M106" s="13" t="n"/>
       <c r="N106" s="13" t="n"/>
@@ -6479,7 +6696,9 @@
         </is>
       </c>
       <c r="J107" s="9" t="n"/>
-      <c r="K107" s="10" t="inlineStr"/>
+      <c r="K107" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L107" s="9" t="n"/>
       <c r="M107" s="9" t="n"/>
       <c r="N107" s="9" t="n"/>
@@ -6530,7 +6749,9 @@
         </is>
       </c>
       <c r="J108" s="13" t="n"/>
-      <c r="K108" s="14" t="inlineStr"/>
+      <c r="K108" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L108" s="13" t="n"/>
       <c r="M108" s="13" t="n"/>
       <c r="N108" s="13" t="n"/>
@@ -6577,7 +6798,9 @@
       </c>
       <c r="I109" s="8" t="inlineStr"/>
       <c r="J109" s="9" t="n"/>
-      <c r="K109" s="8" t="inlineStr"/>
+      <c r="K109" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L109" s="9" t="n"/>
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
@@ -6616,7 +6839,9 @@
       <c r="H110" s="12" t="inlineStr"/>
       <c r="I110" s="12" t="inlineStr"/>
       <c r="J110" s="13" t="n"/>
-      <c r="K110" s="12" t="inlineStr"/>
+      <c r="K110" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -433,6 +433,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -554,15 +572,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -576,46 +609,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -626,11 +699,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -645,31 +726,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -678,11 +783,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 시작일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 시작일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-10
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
@@ -691,11 +804,19 @@
 • 비워두면: 미착수 상태
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-24
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
@@ -705,28 +826,45 @@
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1044,7 +1182,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="88" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -1065,7 +1203,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="83" t="inlineStr">
+      <c r="A2" s="89" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1083,9 +1221,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="84" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:44</t>
+      <c r="O2" s="90" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -130,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -210,11 +210,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -488,6 +517,17 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1182,7 +1222,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="88" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -1203,7 +1243,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="92" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1218,14 +1258,14 @@
       <c r="I2" s="16" t="n"/>
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
-      <c r="L2" s="16" t="n"/>
-      <c r="M2" s="16" t="n"/>
-      <c r="N2" s="17" t="n"/>
-      <c r="O2" s="90" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="93" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:58</t>
+        </is>
+      </c>
+      <c r="N2" s="94" t="n"/>
+      <c r="O2" s="95" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -7497,9 +7537,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="N5:N109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -841,7 +850,10 @@
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
 • 부서가 ★실제로 작업을 시작한 날짜★ 기입
 • PO 후 작업 착수일 (지시 받은 날 아님)
-• 비워두면: 미착수 상태
+📋 입력값 의미:
+  ▸ 빈 칸 → 미착수 또는 '해당없음'
+           (부서 자체가 해당없음이면 PMS에서 '제외' 선택 권장)
+  ▸ 날짜 → 시작 (부서 진척률 50% 인식)
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
         </r>
@@ -862,7 +874,10 @@
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
 • 부서 작업이 ★실제로 완료된 날짜★ 기입
 • 예정일 아닌 ★실제 완료일★ 만 입력
-• 비워두면: PMS 진행현황에서 '미완료'로 집계
+📋 입력값 의미:
+  ▸ 빈 칸 → 미완료 또는 '해당없음'
+           (부서 자체가 해당없음이면 PMS에서 '제외' 선택 권장)
+  ▸ 날짜 → 완료 (부서 진척률 100%)
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
@@ -1215,14 +1230,14 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" style="43" min="12" max="12"/>
-    <col width="12" customWidth="1" style="43" min="13" max="13"/>
+    <col width="5" customWidth="1" style="43" min="12" max="12"/>
+    <col width="5" customWidth="1" style="43" min="13" max="13"/>
     <col width="10" customWidth="1" style="43" min="14" max="14"/>
     <col width="28" customWidth="1" style="43" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="91" t="inlineStr">
+      <c r="A1" s="96" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -1243,7 +1258,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="92" t="inlineStr">
+      <c r="A2" s="97" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1259,13 +1274,13 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="93" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:58</t>
-        </is>
-      </c>
-      <c r="N2" s="94" t="n"/>
-      <c r="O2" s="95" t="n"/>
+      <c r="M2" s="98" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="N2" s="16" t="n"/>
+      <c r="O2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1230,14 +1239,14 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" style="43" min="12" max="12"/>
-    <col width="5" customWidth="1" style="43" min="13" max="13"/>
+    <col width="7" customWidth="1" style="43" min="12" max="12"/>
+    <col width="7" customWidth="1" style="43" min="13" max="13"/>
     <col width="10" customWidth="1" style="43" min="14" max="14"/>
     <col width="28" customWidth="1" style="43" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="96" t="inlineStr">
+      <c r="A1" s="99" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -1258,7 +1267,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="97" t="inlineStr">
+      <c r="A2" s="100" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1274,9 +1283,9 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="98" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="M2" s="101" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="N2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1246,7 +1255,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -1267,7 +1276,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="100" t="inlineStr">
+      <c r="A2" s="103" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1283,9 +1292,9 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="101" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="M2" s="104" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="N2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1255,7 +1264,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="102" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 제조기술1팀 │ 2026</t>
         </is>
@@ -1276,7 +1285,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="103" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 제조기술1팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1292,9 +1301,9 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="104" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="M2" s="107" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:58</t>
         </is>
       </c>
       <c r="N2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -648,30 +648,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -685,86 +670,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -775,19 +720,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -802,55 +739,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -859,19 +772,11 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 시작일
+        <t>▣ 부서 시작일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-10
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
@@ -883,19 +788,11 @@
   ▸ 날짜 → 시작 (부서 진척률 50% 인식)
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 완료일
+        <t>▣ 부서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-24
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
@@ -908,45 +805,28 @@
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1476,7 +1356,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1582,7 +1462,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1688,7 +1568,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1741,7 +1621,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1794,7 +1674,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1847,7 +1727,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1900,7 +1780,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1953,7 +1833,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -2006,7 +1886,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -2059,7 +1939,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -2112,7 +1992,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2165,7 +2045,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -2218,7 +2098,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2271,7 +2151,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2324,7 +2204,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2377,7 +2257,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2430,7 +2310,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2483,7 +2363,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2536,7 +2416,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2589,7 +2469,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2642,7 +2522,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2801,7 +2681,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2854,7 +2734,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2907,7 +2787,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2960,7 +2840,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -3013,7 +2893,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -3066,7 +2946,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -3172,7 +3052,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -3225,7 +3105,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -3278,7 +3158,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -3437,7 +3317,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3490,7 +3370,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -3543,7 +3423,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3596,7 +3476,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3649,7 +3529,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3702,7 +3582,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3808,7 +3688,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3861,7 +3741,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3914,7 +3794,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -3967,7 +3847,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -4020,7 +3900,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -4073,7 +3953,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -4126,7 +4006,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -4179,7 +4059,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -4232,7 +4112,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -4285,7 +4165,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -4338,7 +4218,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -4444,7 +4324,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4497,7 +4377,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -4550,7 +4430,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -4603,7 +4483,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4709,7 +4589,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4762,7 +4642,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -4815,7 +4695,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4868,7 +4748,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -4921,7 +4801,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4974,7 +4854,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -5027,7 +4907,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -5080,7 +4960,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -5133,7 +5013,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -5239,7 +5119,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -5292,7 +5172,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -5345,7 +5225,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -5398,7 +5278,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5451,7 +5331,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -5504,7 +5384,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5557,7 +5437,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -5610,7 +5490,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5769,7 +5649,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5822,7 +5702,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5875,7 +5755,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5928,7 +5808,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5981,7 +5861,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -6087,7 +5967,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -6140,7 +6020,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -6193,7 +6073,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -6246,7 +6126,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -6299,7 +6179,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -6352,7 +6232,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6405,7 +6285,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -6458,7 +6338,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6564,7 +6444,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6617,7 +6497,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -6670,7 +6550,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6723,7 +6603,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -6776,7 +6656,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -6829,7 +6709,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6935,7 +6815,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -7037,7 +6917,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
